--- a/templates/excel/MatchAid_PointScoring_3x6_Template.xlsx
+++ b/templates/excel/MatchAid_PointScoring_3x6_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bc09bc27ca3c1c/Documents/GitHub/MatchAid_GoDaddy/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE6B3AD8-6088-4DC0-8503-F47776CB08A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{DE6B3AD8-6088-4DC0-8503-F47776CB08A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D876E35-FCDF-4248-AFBA-FF5DF6319CE5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +190,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -617,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -670,9 +676,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -709,20 +712,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -730,14 +727,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -761,6 +764,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -778,6 +787,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1053,9 +1066,9 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1067,13 +1080,13 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="33"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="37"/>
     </row>
     <row r="4" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="8" t="s">
         <v>6</v>
       </c>
@@ -1085,13 +1098,13 @@
       <c r="J4" s="9"/>
       <c r="K4" s="10"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="34"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="38"/>
     </row>
     <row r="5" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1103,13 +1116,13 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="34"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="38"/>
     </row>
     <row r="6" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
@@ -1121,13 +1134,13 @@
       <c r="J6" s="9"/>
       <c r="K6" s="10"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="34"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="38"/>
     </row>
     <row r="7" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1139,13 +1152,13 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="34"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="38"/>
     </row>
     <row r="8" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
@@ -1157,13 +1170,13 @@
       <c r="J8" s="9"/>
       <c r="K8" s="10"/>
       <c r="L8" s="9"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="34"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="38"/>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="5" t="s">
         <v>7</v>
       </c>
@@ -1175,13 +1188,13 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="34"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="38"/>
     </row>
     <row r="10" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="8" t="s">
         <v>6</v>
       </c>
@@ -1193,16 +1206,16 @@
       <c r="J10" s="9"/>
       <c r="K10" s="10"/>
       <c r="L10" s="9"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="35"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="39"/>
     </row>
     <row r="11" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -1263,9 +1276,9 @@
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
@@ -1277,13 +1290,13 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="33"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="37"/>
     </row>
     <row r="15" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="8" t="s">
         <v>6</v>
       </c>
@@ -1295,13 +1308,13 @@
       <c r="J15" s="9"/>
       <c r="K15" s="10"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="34"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="38"/>
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="5" t="s">
         <v>7</v>
       </c>
@@ -1313,13 +1326,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="34"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="38"/>
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
       <c r="D17" s="8" t="s">
         <v>6</v>
       </c>
@@ -1331,13 +1344,13 @@
       <c r="J17" s="9"/>
       <c r="K17" s="10"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="34"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="38"/>
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="5" t="s">
         <v>7</v>
       </c>
@@ -1349,13 +1362,13 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="34"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="38"/>
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
       <c r="D19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1367,13 +1380,13 @@
       <c r="J19" s="9"/>
       <c r="K19" s="10"/>
       <c r="L19" s="9"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="34"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="38"/>
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="5" t="s">
         <v>7</v>
       </c>
@@ -1385,13 +1398,13 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="34"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="38"/>
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="8" t="s">
         <v>6</v>
       </c>
@@ -1403,16 +1416,16 @@
       <c r="J21" s="9"/>
       <c r="K21" s="10"/>
       <c r="L21" s="9"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="35"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="39"/>
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -1458,9 +1471,9 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
       <c r="D25" s="5" t="s">
         <v>7</v>
       </c>
@@ -1472,13 +1485,13 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="33"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="37"/>
     </row>
     <row r="26" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
       <c r="D26" s="8" t="s">
         <v>6</v>
       </c>
@@ -1490,13 +1503,13 @@
       <c r="J26" s="9"/>
       <c r="K26" s="10"/>
       <c r="L26" s="9"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="34"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="38"/>
     </row>
     <row r="27" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="5" t="s">
         <v>7</v>
       </c>
@@ -1508,13 +1521,13 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="7"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="34"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="38"/>
     </row>
     <row r="28" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
       <c r="D28" s="8" t="s">
         <v>6</v>
       </c>
@@ -1526,13 +1539,13 @@
       <c r="J28" s="9"/>
       <c r="K28" s="10"/>
       <c r="L28" s="9"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="34"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="38"/>
     </row>
     <row r="29" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
       <c r="D29" s="5" t="s">
         <v>7</v>
       </c>
@@ -1544,13 +1557,13 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="7"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="34"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="38"/>
     </row>
     <row r="30" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="8" t="s">
         <v>6</v>
       </c>
@@ -1562,13 +1575,13 @@
       <c r="J30" s="9"/>
       <c r="K30" s="10"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="34"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="38"/>
     </row>
     <row r="31" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
       <c r="D31" s="5" t="s">
         <v>7</v>
       </c>
@@ -1580,13 +1593,13 @@
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="7"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="34"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="38"/>
     </row>
     <row r="32" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="8" t="s">
         <v>6</v>
       </c>
@@ -1598,16 +1611,16 @@
       <c r="J32" s="9"/>
       <c r="K32" s="10"/>
       <c r="L32" s="9"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="35"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="39"/>
     </row>
     <row r="33" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -1621,186 +1634,153 @@
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="47" t="s">
+      <c r="A35" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="48"/>
+      <c r="B35" s="47"/>
       <c r="C35" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G35" s="28" t="s">
+      <c r="G35" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="29" t="s">
+      <c r="H35" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="I35" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="L35" s="47" t="s">
+      <c r="L35" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="M35" s="48"/>
+      <c r="M35" s="47"/>
       <c r="N35" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="41">
-        <f>Table1_Player1_Quota</f>
+      <c r="A36" s="48">
+        <f>B3</f>
         <v>0</v>
       </c>
-      <c r="B36" s="42"/>
+      <c r="B36" s="49"/>
       <c r="C36" s="13">
-        <f>IF(A36&lt;&gt;"",SUMIF(B3:B10,A36),"")</f>
+        <f>C3</f>
         <v>0</v>
       </c>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="26"/>
-      <c r="L36" s="41" t="s">
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="25"/>
+      <c r="L36" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="M36" s="42"/>
+      <c r="M36" s="41"/>
       <c r="N36" s="13">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="41">
-        <f>Table1_Player2_Quota</f>
+      <c r="A37" s="48">
+        <f>B5</f>
         <v>0</v>
       </c>
-      <c r="B37" s="42"/>
-      <c r="C37" s="17"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="13">
+        <f>C5</f>
+        <v>0</v>
+      </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
       <c r="H37" s="12"/>
       <c r="I37" s="17"/>
-      <c r="L37" s="41" t="s">
+      <c r="L37" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M37" s="42"/>
+      <c r="M37" s="41"/>
       <c r="N37" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="41">
-        <f>Table1_Player3_Quota</f>
+      <c r="A38" s="48">
+        <f>B7</f>
         <v>0</v>
       </c>
-      <c r="B38" s="42"/>
-      <c r="C38" s="17"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="13">
+        <f>C7</f>
+        <v>0</v>
+      </c>
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
       <c r="H38" s="12"/>
       <c r="I38" s="17"/>
-      <c r="L38" s="41" t="s">
+      <c r="L38" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="M38" s="42"/>
+      <c r="M38" s="41"/>
       <c r="N38" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="41">
-        <f>Table1_Player4_Quota</f>
+      <c r="A39" s="48">
+        <f>B9</f>
         <v>0</v>
       </c>
-      <c r="B39" s="42"/>
-      <c r="C39" s="18"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="L39" s="41" t="s">
+      <c r="B39" s="49"/>
+      <c r="C39" s="13">
+        <f>C9</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20"/>
+      <c r="L39" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="M39" s="42"/>
+      <c r="M39" s="41"/>
       <c r="N39" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="46"/>
-      <c r="C40" s="22">
+      <c r="B40" s="45"/>
+      <c r="C40" s="21">
         <f>SUM(C36:C39)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="L40" s="41" t="s">
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="L40" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="M40" s="42"/>
+      <c r="M40" s="41"/>
       <c r="N40" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L41" s="43" t="s">
+      <c r="L41" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="M41" s="44"/>
+      <c r="M41" s="43"/>
       <c r="N41" s="14">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="M25:M32"/>
-    <mergeCell ref="N25:N32"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C14:C15"/>
     <mergeCell ref="M3:M10"/>
     <mergeCell ref="N3:N10"/>
     <mergeCell ref="A14:A15"/>
@@ -1817,6 +1797,48 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="M25:M32"/>
+    <mergeCell ref="N25:N32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.53" bottom="0.22" header="0.22" footer="0.18"/>

--- a/templates/excel/MatchAid_PointScoring_3x6_Template.xlsx
+++ b/templates/excel/MatchAid_PointScoring_3x6_Template.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bc09bc27ca3c1c/Documents/GitHub/MatchAid_GoDaddy/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{DE6B3AD8-6088-4DC0-8503-F47776CB08A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D876E35-FCDF-4248-AFBA-FF5DF6319CE5}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{DE6B3AD8-6088-4DC0-8503-F47776CB08A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677EB52D-FB3A-4E65-957E-0AE2433D81FC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11508" yWindow="-12" windowWidth="11544" windowHeight="13704" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="Group_PlayerKey" localSheetId="0">'Group Template'!$B$1</definedName>
+    <definedName name="Group_TeeTime" localSheetId="0">'Group Template'!$D$1</definedName>
     <definedName name="Table1" localSheetId="0">'Group Template'!$A$2:$N$11</definedName>
     <definedName name="Table1_Hole01" localSheetId="0">'Group Template'!$E$2</definedName>
     <definedName name="Table1_Hole02" localSheetId="0">'Group Template'!$F$2</definedName>
@@ -93,10 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="23">
-  <si>
-    <t>Group</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="24">
   <si>
     <t>Pos</t>
   </si>
@@ -162,13 +160,19 @@
   </si>
   <si>
     <t>PLAYER</t>
+  </si>
+  <si>
+    <t>Group:</t>
+  </si>
+  <si>
+    <t>TeeTime:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +197,20 @@
     </font>
     <font>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -242,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -619,11 +637,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -712,36 +741,33 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -771,6 +797,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1028,23 +1069,25 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="C1" s="49" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1053,24 +1096,24 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -1080,15 +1123,15 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="37"/>
-    </row>
-    <row r="4" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="32"/>
+    </row>
+    <row r="4" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="35"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
@@ -1098,15 +1141,15 @@
       <c r="J4" s="9"/>
       <c r="K4" s="10"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="38"/>
-    </row>
-    <row r="5" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="33"/>
+    </row>
+    <row r="5" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
       <c r="D5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -1116,15 +1159,15 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="38"/>
-    </row>
-    <row r="6" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="33"/>
+    </row>
+    <row r="6" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="35"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -1134,15 +1177,15 @@
       <c r="J6" s="9"/>
       <c r="K6" s="10"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="38"/>
-    </row>
-    <row r="7" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="33"/>
+    </row>
+    <row r="7" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="34"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
       <c r="D7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1152,15 +1195,15 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="38"/>
-    </row>
-    <row r="8" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="33"/>
+    </row>
+    <row r="8" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="35"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
       <c r="D8" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -1170,15 +1213,15 @@
       <c r="J8" s="9"/>
       <c r="K8" s="10"/>
       <c r="L8" s="9"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="38"/>
-    </row>
-    <row r="9" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="33"/>
+    </row>
+    <row r="9" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="34"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
       <c r="D9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -1188,15 +1231,15 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="38"/>
-    </row>
-    <row r="10" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="33"/>
+    </row>
+    <row r="10" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="35"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
       <c r="D10" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -1206,16 +1249,16 @@
       <c r="J10" s="9"/>
       <c r="K10" s="10"/>
       <c r="L10" s="9"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="39"/>
-    </row>
-    <row r="11" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="53"/>
+    </row>
+    <row r="11" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -1224,8 +1267,11 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="M11" s="50">
+        <f>QUOTIENT(C40,3)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="51"/>
     </row>
     <row r="12" spans="1:14" s="4" customFormat="1" ht="7.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
@@ -1245,16 +1291,16 @@
     </row>
     <row r="13" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1263,24 +1309,24 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -1290,15 +1336,15 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="37"/>
-    </row>
-    <row r="15" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="34"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="32"/>
+    </row>
+    <row r="15" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="35"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -1308,15 +1354,15 @@
       <c r="J15" s="9"/>
       <c r="K15" s="10"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="38"/>
-    </row>
-    <row r="16" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="33"/>
+    </row>
+    <row r="16" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="34"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
       <c r="D16" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -1326,15 +1372,15 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="38"/>
-    </row>
-    <row r="17" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="33"/>
+    </row>
+    <row r="17" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="35"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
       <c r="D17" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -1344,15 +1390,15 @@
       <c r="J17" s="9"/>
       <c r="K17" s="10"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="38"/>
-    </row>
-    <row r="18" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="33"/>
+    </row>
+    <row r="18" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="34"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
       <c r="D18" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -1362,15 +1408,15 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="38"/>
-    </row>
-    <row r="19" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="33"/>
+    </row>
+    <row r="19" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="35"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
       <c r="D19" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -1380,15 +1426,15 @@
       <c r="J19" s="9"/>
       <c r="K19" s="10"/>
       <c r="L19" s="9"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="38"/>
-    </row>
-    <row r="20" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="33"/>
+    </row>
+    <row r="20" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="34"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
       <c r="D20" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -1398,15 +1444,15 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="38"/>
-    </row>
-    <row r="21" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="33"/>
+    </row>
+    <row r="21" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="35"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
       <c r="D21" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -1416,16 +1462,16 @@
       <c r="J21" s="9"/>
       <c r="K21" s="10"/>
       <c r="L21" s="9"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="39"/>
-    </row>
-    <row r="22" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="53"/>
+    </row>
+    <row r="22" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -1434,22 +1480,25 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="M22" s="50">
+        <f>QUOTIENT(C40,3)+IF(MOD(C40,3)=2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="51"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1458,24 +1507,24 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="25" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
       <c r="D25" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -1485,15 +1534,15 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="37"/>
-    </row>
-    <row r="26" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="32"/>
+    </row>
+    <row r="26" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="35"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -1503,15 +1552,15 @@
       <c r="J26" s="9"/>
       <c r="K26" s="10"/>
       <c r="L26" s="9"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="38"/>
-    </row>
-    <row r="27" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="33"/>
+    </row>
+    <row r="27" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
       <c r="D27" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -1521,15 +1570,15 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="7"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="38"/>
-    </row>
-    <row r="28" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="34"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="33"/>
+    </row>
+    <row r="28" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="35"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -1539,15 +1588,15 @@
       <c r="J28" s="9"/>
       <c r="K28" s="10"/>
       <c r="L28" s="9"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="38"/>
-    </row>
-    <row r="29" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="33"/>
+    </row>
+    <row r="29" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="34"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
       <c r="D29" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -1557,15 +1606,15 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="7"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="38"/>
-    </row>
-    <row r="30" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="34"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="33"/>
+    </row>
+    <row r="30" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="35"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -1575,15 +1624,15 @@
       <c r="J30" s="9"/>
       <c r="K30" s="10"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="38"/>
-    </row>
-    <row r="31" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="33"/>
+    </row>
+    <row r="31" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="34"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
       <c r="D31" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1593,15 +1642,15 @@
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="7"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="38"/>
-    </row>
-    <row r="32" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="34"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="33"/>
+    </row>
+    <row r="32" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="35"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
       <c r="D32" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
@@ -1611,16 +1660,16 @@
       <c r="J32" s="9"/>
       <c r="K32" s="10"/>
       <c r="L32" s="9"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="39"/>
-    </row>
-    <row r="33" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="53"/>
+    </row>
+    <row r="33" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -1629,44 +1678,47 @@
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
+      <c r="M33" s="50">
+        <f>QUOTIENT(C40,3)+IF(MOD(C40,3)&gt;=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="51"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="47"/>
+      <c r="A35" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="46"/>
       <c r="C35" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="47"/>
+      <c r="M35" s="46"/>
       <c r="N35" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48">
+      <c r="A36" s="47">
         <f>B3</f>
         <v>0</v>
       </c>
-      <c r="B36" s="49"/>
+      <c r="B36" s="48"/>
       <c r="C36" s="13">
         <f>C3</f>
         <v>0</v>
@@ -1675,20 +1727,20 @@
       <c r="G36" s="23"/>
       <c r="H36" s="24"/>
       <c r="I36" s="25"/>
-      <c r="L36" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="M36" s="41"/>
+      <c r="L36" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="M36" s="40"/>
       <c r="N36" s="13">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48">
+      <c r="A37" s="47">
         <f>B5</f>
         <v>0</v>
       </c>
-      <c r="B37" s="49"/>
+      <c r="B37" s="48"/>
       <c r="C37" s="13">
         <f>C5</f>
         <v>0</v>
@@ -1697,20 +1749,20 @@
       <c r="G37" s="16"/>
       <c r="H37" s="12"/>
       <c r="I37" s="17"/>
-      <c r="L37" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="M37" s="41"/>
+      <c r="L37" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="40"/>
       <c r="N37" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48">
+      <c r="A38" s="47">
         <f>B7</f>
         <v>0</v>
       </c>
-      <c r="B38" s="49"/>
+      <c r="B38" s="48"/>
       <c r="C38" s="13">
         <f>C7</f>
         <v>0</v>
@@ -1719,20 +1771,20 @@
       <c r="G38" s="16"/>
       <c r="H38" s="12"/>
       <c r="I38" s="17"/>
-      <c r="L38" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="M38" s="41"/>
+      <c r="L38" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="M38" s="40"/>
       <c r="N38" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48">
+      <c r="A39" s="47">
         <f>B9</f>
         <v>0</v>
       </c>
-      <c r="B39" s="49"/>
+      <c r="B39" s="48"/>
       <c r="C39" s="13">
         <f>C9</f>
         <v>0</v>
@@ -1741,19 +1793,19 @@
       <c r="G39" s="18"/>
       <c r="H39" s="19"/>
       <c r="I39" s="20"/>
-      <c r="L39" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="M39" s="41"/>
+      <c r="L39" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="M39" s="40"/>
       <c r="N39" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="45"/>
+      <c r="A40" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="44"/>
       <c r="C40" s="21">
         <f>SUM(C36:C39)</f>
         <v>0</v>
@@ -1762,25 +1814,67 @@
       <c r="G40" s="22"/>
       <c r="H40" s="22"/>
       <c r="I40" s="22"/>
-      <c r="L40" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="M40" s="41"/>
+      <c r="L40" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="M40" s="40"/>
       <c r="N40" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L41" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="M41" s="43"/>
+      <c r="L41" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="42"/>
       <c r="N41" s="14">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="M25:M32"/>
+    <mergeCell ref="N25:N32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C14:C15"/>
     <mergeCell ref="M3:M10"/>
     <mergeCell ref="N3:N10"/>
     <mergeCell ref="A14:A15"/>
@@ -1797,48 +1891,6 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="M25:M32"/>
-    <mergeCell ref="N25:N32"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.53" bottom="0.22" header="0.22" footer="0.18"/>

--- a/templates/excel/MatchAid_PointScoring_3x6_Template.xlsx
+++ b/templates/excel/MatchAid_PointScoring_3x6_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bc09bc27ca3c1c/Documents/GitHub/MatchAid_GoDaddy/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{DE6B3AD8-6088-4DC0-8503-F47776CB08A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677EB52D-FB3A-4E65-957E-0AE2433D81FC}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{DE6B3AD8-6088-4DC0-8503-F47776CB08A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BB8DE93-C8F3-40B8-BBF5-8E4CB328C81A}"/>
   <bookViews>
-    <workbookView xWindow="11508" yWindow="-12" windowWidth="11544" windowHeight="13704" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group Template" sheetId="1" r:id="rId1"/>
@@ -28,15 +28,19 @@
     <definedName name="Table1_Player1_DisplayName" localSheetId="0">'Group Template'!$B$3</definedName>
     <definedName name="Table1_Player1_PairingPos" localSheetId="0">'Group Template'!$A$3</definedName>
     <definedName name="Table1_Player1_Quota" localSheetId="0">'Group Template'!$C$3</definedName>
+    <definedName name="Table1_Player1_TeeSetName" localSheetId="0">'Group Template'!$C$36</definedName>
     <definedName name="Table1_Player2_DisplayName" localSheetId="0">'Group Template'!$B$5</definedName>
     <definedName name="Table1_Player2_PairingPos" localSheetId="0">'Group Template'!$A$5</definedName>
     <definedName name="Table1_Player2_Quota" localSheetId="0">'Group Template'!$C$5</definedName>
+    <definedName name="Table1_Player2_TeeSetName" localSheetId="0">'Group Template'!$C$37</definedName>
     <definedName name="Table1_Player3_DisplayName" localSheetId="0">'Group Template'!$B$7</definedName>
     <definedName name="Table1_Player3_PairingPos" localSheetId="0">'Group Template'!$A$7</definedName>
     <definedName name="Table1_Player3_Quota" localSheetId="0">'Group Template'!$C$7</definedName>
+    <definedName name="Table1_Player3_TeeSetName" localSheetId="0">'Group Template'!$C$38</definedName>
     <definedName name="Table1_Player4_DisplayName" localSheetId="0">'Group Template'!$B$9</definedName>
     <definedName name="Table1_Player4_PairingPos" localSheetId="0">'Group Template'!$A$9</definedName>
     <definedName name="Table1_Player4_Quota" localSheetId="0">'Group Template'!$C$9</definedName>
+    <definedName name="Table1_Player4_TeeSetName" localSheetId="0">'Group Template'!$C$39</definedName>
     <definedName name="Table2" localSheetId="0">'Group Template'!$A$13:$N$22</definedName>
     <definedName name="Table2_Hole01" localSheetId="0">'Group Template'!$E$13</definedName>
     <definedName name="Table2_Hole02" localSheetId="0">'Group Template'!$F$13</definedName>
@@ -94,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="25">
   <si>
     <t>Pos</t>
   </si>
@@ -166,6 +170,9 @@
   </si>
   <si>
     <t>TeeTime:</t>
+  </si>
+  <si>
+    <t>TEE SET</t>
   </si>
 </sst>
 </file>
@@ -182,18 +189,21 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -260,7 +270,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -359,7 +369,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -373,60 +383,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -439,39 +395,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
@@ -486,76 +416,7 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
@@ -645,6 +506,258 @@
       <top/>
       <bottom style="double">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,7 +765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -687,9 +800,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -699,59 +809,23 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -759,14 +833,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -774,43 +857,106 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1072,7 +1218,7 @@
         <v>22</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1109,9 +1255,9 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1123,13 +1269,13 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="32"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="26"/>
     </row>
     <row r="4" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="8" t="s">
         <v>5</v>
       </c>
@@ -1141,13 +1287,13 @@
       <c r="J4" s="9"/>
       <c r="K4" s="10"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="33"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="27"/>
     </row>
     <row r="5" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
@@ -1159,13 +1305,13 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="33"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="27"/>
     </row>
     <row r="6" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="35"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1177,13 +1323,13 @@
       <c r="J6" s="9"/>
       <c r="K6" s="10"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="33"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="27"/>
     </row>
     <row r="7" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1195,13 +1341,13 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="33"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="35"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="8" t="s">
         <v>5</v>
       </c>
@@ -1213,13 +1359,13 @@
       <c r="J8" s="9"/>
       <c r="K8" s="10"/>
       <c r="L8" s="9"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="33"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1231,13 +1377,13 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="33"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="35"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="8" t="s">
         <v>5</v>
       </c>
@@ -1249,16 +1395,16 @@
       <c r="J10" s="9"/>
       <c r="K10" s="10"/>
       <c r="L10" s="9"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="53"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -1267,11 +1413,11 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
-      <c r="M11" s="50">
-        <f>QUOTIENT(C40,3)</f>
+      <c r="M11" s="16">
+        <f>QUOTIENT(E40,3)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="51"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" s="4" customFormat="1" ht="7.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
@@ -1322,9 +1468,9 @@
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="5" t="s">
         <v>6</v>
       </c>
@@ -1336,13 +1482,13 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="32"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="35"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="8" t="s">
         <v>5</v>
       </c>
@@ -1354,13 +1500,13 @@
       <c r="J15" s="9"/>
       <c r="K15" s="10"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="33"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="34"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="5" t="s">
         <v>6</v>
       </c>
@@ -1372,13 +1518,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="33"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="35"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="8" t="s">
         <v>5</v>
       </c>
@@ -1390,13 +1536,13 @@
       <c r="J17" s="9"/>
       <c r="K17" s="10"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="33"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="27"/>
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1408,13 +1554,13 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="33"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="35"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="8" t="s">
         <v>5</v>
       </c>
@@ -1426,13 +1572,13 @@
       <c r="J19" s="9"/>
       <c r="K19" s="10"/>
       <c r="L19" s="9"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="33"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="27"/>
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="5" t="s">
         <v>6</v>
       </c>
@@ -1444,13 +1590,13 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="33"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="27"/>
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="35"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="8" t="s">
         <v>5</v>
       </c>
@@ -1462,16 +1608,16 @@
       <c r="J21" s="9"/>
       <c r="K21" s="10"/>
       <c r="L21" s="9"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="53"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="28"/>
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -1480,11 +1626,11 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
-      <c r="M22" s="50">
-        <f>QUOTIENT(C40,3)+IF(MOD(C40,3)=2,1,0)</f>
+      <c r="M22" s="16">
+        <f>QUOTIENT(E40,3)+IF(MOD(E40,3)=2,1,0)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="51"/>
+      <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1520,9 +1666,9 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="5" t="s">
         <v>6</v>
       </c>
@@ -1534,13 +1680,13 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="32"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="26"/>
     </row>
     <row r="26" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="35"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="8" t="s">
         <v>5</v>
       </c>
@@ -1552,13 +1698,13 @@
       <c r="J26" s="9"/>
       <c r="K26" s="10"/>
       <c r="L26" s="9"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="33"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="34"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="5" t="s">
         <v>6</v>
       </c>
@@ -1570,13 +1716,13 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="7"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="33"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="35"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="8" t="s">
         <v>5</v>
       </c>
@@ -1588,13 +1734,13 @@
       <c r="J28" s="9"/>
       <c r="K28" s="10"/>
       <c r="L28" s="9"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="33"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="27"/>
     </row>
     <row r="29" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="34"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
       <c r="D29" s="5" t="s">
         <v>6</v>
       </c>
@@ -1606,13 +1752,13 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="7"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="33"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="35"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="8" t="s">
         <v>5</v>
       </c>
@@ -1624,13 +1770,13 @@
       <c r="J30" s="9"/>
       <c r="K30" s="10"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="33"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="27"/>
     </row>
     <row r="31" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
       <c r="D31" s="5" t="s">
         <v>6</v>
       </c>
@@ -1642,13 +1788,13 @@
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="7"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="33"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="35"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1660,16 +1806,16 @@
       <c r="J32" s="9"/>
       <c r="K32" s="10"/>
       <c r="L32" s="9"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="53"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="28"/>
     </row>
     <row r="33" spans="1:14" ht="25.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -1678,203 +1824,178 @@
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
-      <c r="M33" s="50">
-        <f>QUOTIENT(C40,3)+IF(MOD(C40,3)&gt;=1,1,0)</f>
+      <c r="M33" s="16">
+        <f>QUOTIENT(E40,3)+IF(MOD(E40,3)&gt;=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="51"/>
-    </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="N33" s="17"/>
+    </row>
+    <row r="34" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="45" t="s">
+      <c r="A35" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="15" t="s">
+      <c r="B35" s="53"/>
+      <c r="C35" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="54"/>
+      <c r="E35" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="G35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="H35" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="I35" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="29" t="s">
+      <c r="J35" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L35" s="45" t="s">
+      <c r="L35" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="M35" s="46"/>
-      <c r="N35" s="15" t="s">
+      <c r="M35" s="34"/>
+      <c r="N35" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="47">
+      <c r="A36" s="56">
         <f>B3</f>
         <v>0</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="13">
+      <c r="B36" s="51"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="45">
         <f>C3</f>
         <v>0</v>
       </c>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="25"/>
-      <c r="L36" s="39" t="s">
+      <c r="G36" s="44"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M36" s="40"/>
-      <c r="N36" s="13">
+      <c r="M36" s="30"/>
+      <c r="N36" s="12">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="47">
+      <c r="A37" s="56">
         <f>B5</f>
         <v>0</v>
       </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="13">
+      <c r="B37" s="51"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="45">
         <f>C5</f>
         <v>0</v>
       </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="17"/>
-      <c r="L37" s="39" t="s">
+      <c r="G37" s="46"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="47"/>
+      <c r="L37" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="M37" s="40"/>
-      <c r="N37" s="13">
+      <c r="M37" s="30"/>
+      <c r="N37" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="47">
+      <c r="A38" s="56">
         <f>B7</f>
         <v>0</v>
       </c>
-      <c r="B38" s="48"/>
-      <c r="C38" s="13">
+      <c r="B38" s="51"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="45">
         <f>C7</f>
         <v>0</v>
       </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="17"/>
-      <c r="L38" s="39" t="s">
+      <c r="G38" s="46"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="47"/>
+      <c r="L38" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="M38" s="40"/>
-      <c r="N38" s="13">
+      <c r="M38" s="30"/>
+      <c r="N38" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="47">
+    <row r="39" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="60">
         <f>B9</f>
         <v>0</v>
       </c>
-      <c r="B39" s="48"/>
-      <c r="C39" s="13">
+      <c r="B39" s="61"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="62">
         <f>C9</f>
         <v>0</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20"/>
-      <c r="L39" s="39" t="s">
+      <c r="G39" s="48"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="50"/>
+      <c r="L39" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M39" s="40"/>
-      <c r="N39" s="13">
+      <c r="M39" s="30"/>
+      <c r="N39" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="43" t="s">
+    <row r="40" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="44"/>
-      <c r="C40" s="21">
-        <f>SUM(C36:C39)</f>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="59">
+        <f>SUM(E36:E39)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="L40" s="39" t="s">
+      <c r="G40" s="35"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="37"/>
+      <c r="L40" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="M40" s="40"/>
-      <c r="N40" s="13">
+      <c r="M40" s="30"/>
+      <c r="N40" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L41" s="41" t="s">
+    <row r="41" spans="1:14" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L41" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="M41" s="42"/>
-      <c r="N41" s="14">
+      <c r="M41" s="32"/>
+      <c r="N41" s="13">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="M25:M32"/>
-    <mergeCell ref="N25:N32"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C14:C15"/>
+  <mergeCells count="64">
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
     <mergeCell ref="M3:M10"/>
     <mergeCell ref="N3:N10"/>
     <mergeCell ref="A14:A15"/>
@@ -1891,6 +2012,51 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="M25:M32"/>
+    <mergeCell ref="N25:N32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.53" bottom="0.22" header="0.22" footer="0.18"/>
